--- a/src/main/resources/excel/3 - A1.xlsx
+++ b/src/main/resources/excel/3 - A1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="1 A1" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,6 +13,8 @@
     <sheet name="3 A1" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="4 A1" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="5 A1" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="6 A1" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="1 locución adverbial" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="1926">
   <si>
     <t xml:space="preserve">Sweep</t>
   </si>
@@ -1607,159 +1609,6 @@
     <t xml:space="preserve">pliz fɪl ðə bɑks wɪð bʊks.</t>
   </si>
   <si>
-    <t xml:space="preserve">What time is it?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué hora es?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wɑt taɪm ɪz ɪt?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could you tell me the time, please?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Podría decirme la hora, por favor?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kʊd ju tɛl mi ðə taɪm, pliz?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do you have the time?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Tiene la hora?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">du ju hæv ðə taɪm?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can you tell me what time it is?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Puede decirme qué hora es?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kæn ju tɛl mi wɑt taɪm ɪt ɪz?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's one o'clock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es la una.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts wʌn əˈklɑk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's three o'clock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las tres.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts θri əˈklɑk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's half past one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es la una y media. (1:30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts hæf pæst wʌn. (1:30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's half past four.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las cuatro y media. (4:30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts hæf pæst fɔr. (4:30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's quarter past two.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las dos y cuarto. (2:15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts ˈkwɔrtər pæst tu. (2:15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's quarter past five.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las cinco y cuarto. (5:15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts ˈkwɔrtər pæst faɪv. (5:15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's quarter to three.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las tres menos cuarto. (2:45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts ˈkwɔrtər tu θri. (2:45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's quarter to six.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las seis menos cuarto. (5:45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts ˈkwɔrtər tu sɪks. (5:45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's ten minutes past seven.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las siete y diez. (7:10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts tɛn ˈmɪnəts pæst ˈsɛvən. (7:10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's twenty minutes past eight.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las ocho y veinte. (8:20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts ˈtwɛnti ˈmɪnəts pæst eɪt. (8:20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's twenty minutes to nine.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las nueve menos veinte. (8:40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts ˈtwɛnti ˈmɪnəts tu naɪn. (8:40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's five minutes to ten.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Son las diez menos cinco. (9:55)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts faɪv ˈmɪnəts tu tɛn. (9:55)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please move the folder to the top right corner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por favor, mueva la carpeta a la esquina superior derecha.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pliz muv ðə ˈfoʊldər tu ðə tɑp raɪt ˈkɔrnər.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Can you place the folder in the upper right corner?</t>
   </si>
   <si>
@@ -3444,6 +3293,2517 @@
   </si>
   <si>
     <t xml:space="preserve">wɜrk ɪn ˈpɛrəˌlɛl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈɔlˌmoʊst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I almost forgot your book.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casi olvido tu libro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ ˈɔlˌmoʊst fərˈɡɑt jʊər bʊk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She's almost done with the project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella casi termina con el proyecto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃiz ˈɔlˌmoʊst dʌn wɪð ðə ˈprɑʤɛkt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We're almost there.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya casi llegamos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wir ˈɔlˌmoʊst ðɛr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He almost won the race.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casi gana la carrera.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi ˈɔlˌmoʊst wʌn ðə reɪs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's almost time to go.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya casi es hora de irnos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈɔlˌmoʊst taɪm tu ɡoʊ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolutely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolutamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˌæbsəˈlutli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I absolutely agree with you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estoy totalmente de acuerdo contigo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ ˌæbsəˈlutli əˈɡri wɪð ju.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was absolutely furious.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella estaba absolutamente furiosa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz ˌæbsəˈlutli ˈfjʊriəs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is absolutely the best cake.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este es absolutamente el mejor pastel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðɪs ɪz ˌæbsəˈlutli ðə bɛst keɪk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He is absolutely sure of the answer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Está absolutamente seguro de la respuesta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi ɪz ˌæbsəˈlutli ʃʊr ʌv ði ˈænsər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The show was absolutely wonderful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El espectáculo fue absolutamente maravilloso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ʃoʊ wʌz ˌæbsəˈlutli ˈwʌndərfəl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈbɛrli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I could barely see in the dark.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas podía ver en la oscuridad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ kʊd ˈbɛrli si ɪn ðə dɑrk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She barely passed the exam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas aprobó el examen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˈbɛrli pæst ði ɪɡˈzæm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They barely made it on time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas llegaron a tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ ˈbɛrli meɪd ɪt ɑn taɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He barely speaks to me anymore.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas me habla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi ˈbɛrli spiks tu mi ˌɛniˈmɔr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We barely touched our food.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas tocamos nuestra comida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi ˈbɛrli tʌʧt ˈaʊər fud.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kəmˈplitli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was completely surprised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella estaba completamente sorprendida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz kəmˈplitli sərˈpraɪzd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The room was completely silent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sala estaba completamente en silencio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə rum wʌz kəmˈplitli ˈsaɪlənt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He had completely forgotten the meeting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se había olvidado por completo de la reunión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi hæd kəmˈplitli fərˈɡɑtən ðə ˈmitɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The city was completely deserted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La ciudad estaba completamente desierta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈsɪti wʌz kəmˈplitli dɪˈzɜrtɪd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm completely exhausted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estoy completamente exhausto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪm kəmˈplitli ɪɡˈzɑstɪd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deeply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profundamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈdipli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm deeply sorry for your loss.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamento profundamente tu pérdida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪm ˈdipli ˈsɑri fɔr jʊər lɔs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was deeply involved in the project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella estaba profundamente involucrada en el proyecto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz ˈdipli ɪnˈvɑlvd ɪn ðə ˈprɑʤɛkt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They're deeply in love with each other.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Están profundamente enamorados el uno del otro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðɛr ˈdipli ɪn lʌv wɪð iʧ ˈʌðər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He was deeply offended by the remark.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él se sintió profundamente ofendido por el comentario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi wʌz ˈdipli əˈfɛndɪd baɪ ðə rɪˈmɑrk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We are deeply concerned about the situation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estamos profundamente preocupados por la situación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi ɑr ˈdipli kənˈsɜrnd əˈbaʊt ðə ˌsɪʧuˈeɪʃən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suficiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪˈnʌf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I don't have enough money.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No tengo suficiente dinero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ doʊnt hæv ɪˈnʌf ˈmʌni.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She didn't study enough for the test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella no estudió lo suficiente para el examen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˈdɪdənt ˈstʌdi ɪˈnʌf fɔr ðə tɛst.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He's old enough to make his own decisions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él tiene la edad suficiente para tomar sus propias decisiones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hiz oʊld ɪˈnʌf tu meɪk hɪz oʊn dɪˈsɪʒənz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We've seen enough for today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemos visto suficiente por hoy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wiv sin ɪˈnʌf fɔr təˈdeɪ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There isn't enough space for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No hay suficiente espacio para todos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðɛr ˈɪzənt ɪˈnʌf speɪs fɔr ˈɛvriˌwʌn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entirely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪnˈtaɪərli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That is entirely your decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esa es completamente tu decisión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðæt ɪz ɪnˈtaɪərli jʊər dɪˈsɪʒən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The movie was entirely different from the book.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La película era completamente diferente del libro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈmuvi wʌz ɪnˈtaɪərli ˈdɪfərənt frʌm ðə bʊk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was entirely convinced by his argument.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El argumento de él la convenció completamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz ɪnˈtaɪərli kənˈvɪnst baɪ hɪz ˈɑrɡjəmənt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was entirely my fault.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fue completamente mi culpa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪt wʌz ɪnˈtaɪərli maɪ fɔlt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The approach is entirely new.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El enfoque es completamente nuevo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ði əˈproʊʧ ɪz ɪnˈtaɪərli nu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extremely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extremadamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɛkˈstrimli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is extremely important.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es extremadamente importante.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪt ɪz ɛkˈstrimli ɪmˈpɔrtənt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was extremely happy about the news.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella estaba extremadamente feliz con la noticia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz ɛkˈstrimli ˈhæpi əˈbaʊt ðə nuz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The weather is extremely cold today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El clima es extremadamente frío hoy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈwɛðər ɪz ɛkˈstrimli koʊld təˈdeɪ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That sounds extremely complicated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eso suena extremadamente complicado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðæt saʊndz ɛkˈstrimli ˈkɑmpləˌkeɪtəd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He was driving extremely fast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él estaba conduciendo extremadamente rápido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi wʌz ˈdraɪvɪŋ ɛkˈstrimli fæst.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fairly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bastante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈfɛrli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The test was fairly easy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El examen fue bastante fácil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə tɛst wʌz ˈfɛrli ˈizi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He is fairly certain it will rain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Está bastante seguro de que lloverá.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi ɪz ˈfɛrli ˈsɜrtən ɪt wɪl reɪn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She played the game fairly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella jugó el juego de manera justa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi pleɪd ðə ɡeɪm ˈfɛrli.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The book was fairly interesting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El libro era bastante interesante.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə bʊk wʌz ˈfɛrli ˈɪntrəstɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They were treated fairly at work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los trataban de manera justa en el trabajo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ wɜr ˈtritɪd ˈfɛrli æt wɜrk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈhɑrdli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I hardly know her.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas la conozco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ ˈhɑrdli noʊ hɜr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He could hardly believe his eyes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas podía creer lo que veía.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi kʊd ˈhɑrdli bɪˈliv hɪz aɪz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We hardly ever go out anymore.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya casi nunca salimos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi ˈhɑrdli ˈɛvər ɡoʊ aʊt ˌɛniˈmɔr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She hardly said a word during the meeting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas dijo una palabra durante la reunión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˈhɑrdli sɛd ə wɜrd ˈdʊrɪŋ ðə ˈmitɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's hardly the best solution to the problem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No es la mejor solución al problema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈhɑrdli ðə bɛst səˈluʃən tu ðə ˈprɑbləm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈhaɪli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He is highly respected in his field.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es muy respetado en su campo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi ɪz ˈhaɪli rɪˈspɛktɪd ɪn hɪz fild.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The film was highly entertaining.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La película fue muy entretenida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə fɪlm wʌz ˈhaɪli ˌɛntərˈteɪnɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She is highly skilled at coding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella es muy hábil en la codificación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ɪz ˈhaɪli skɪld æt ˈkoʊdɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This issue is highly sensitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este tema es muy delicado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðɪs ˈɪʃu ɪz ˈhaɪli ˈsɛnsətɪv.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Their proposal was highly successful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Su propuesta fue muy exitosa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðɛr prəˈpoʊzəl wʌz ˈhaɪli səkˈsɛsfəl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Just</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplemente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʤʌst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's just wonderful to see you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es maravilloso verte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ʤʌst ˈwʌndərfəl tu si ju.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That's just what I needed!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¡Eso es justo lo que necesitaba!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðæts ʤʌst wɑt aɪ ˈnidɪd!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She arrived just in time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llegó justo a tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi əˈraɪvd ʤʌst ɪn taɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He was just leaving the house.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él estaba saliendo de la casa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi wʌz ʤʌst ˈlivɪŋ ðə haʊs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They just finished their work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acababan de terminar su trabajo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ ʤʌst ˈfɪnɪʃt ðɛr wɜrk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈmɪrli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was merely a suggestion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fue simplemente una sugerencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪt wʌz ˈmɪrli ə səɡˈʤɛsʧən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was merely curious.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella simplemente tenía curiosidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz ˈmɪrli ˈkjʊriəs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He is merely a child.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él es simplemente un niño.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi ɪz ˈmɪrli ə ʧaɪld.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That was merely luck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eso fue pura suerte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðæt wʌz ˈmɪrli lʌk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They were merely following orders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplemente estaban siguiendo órdenes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ wɜr ˈmɪrli ˈfɑloʊɪŋ ˈɔrdərz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nearly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈnɪrli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She nearly missed the bus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella casi pierde el autobús.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˈnɪrli mɪst ðə bʌs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cup is nearly full.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La taza está casi llena.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə kʌp ɪz ˈnɪrli fʊl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He was nearly asleep when the phone rang.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él estaba casi dormido cuando sonó el teléfono.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi wʌz ˈnɪrli əˈslip wɛn ðə foʊn ræŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We have nearly completed the project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casi hemos completado el proyecto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi hæv ˈnɪrli kəmˈplitɪd ðə ˈprɑʤɛkt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They nearly won the game.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casi ganaron el juego.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ ˈnɪrli wʌn ðə ɡeɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En parte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈpɑrtli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was partly my fault.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En parte fue culpa mía.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪt wʌz ˈpɑrtli maɪ fɔlt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The success was partly due to her efforts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El éxito se debió en parte a sus esfuerzos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə səkˈsɛs wʌz ˈpɑrtli du tu hɜr ˈɛfərts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sky is partly cloudy today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El cielo está parcialmente nublado hoy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə skaɪ ɪz ˈpɑrtli ˈklaʊdi təˈdeɪ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The door was partly open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La puerta estaba parcialmente abierta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə dɔr wʌz ˈpɑrtli ˈoʊpən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was partly responsible for the decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella fue en parte responsable de la decisión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz ˈpɑrtli riˈspɑnsəbəl fɔr ðə dɪˈsɪʒən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfectly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfectamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈpɜrfəktli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The dress fits perfectly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El vestido le queda perfecto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə drɛs fɪts ˈpɜrfəktli.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He speaks English perfectly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él habla inglés perfectamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi spiks ˈɪŋɡlɪʃ ˈpɜrfəktli.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The timing was perfectly planned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El momento fue perfectamente planeado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈtaɪmɪŋ wʌz ˈpɜrfəktli plænd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She understood the instructions perfectly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella entendió las instrucciones perfectamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˌʌndərˈstʊd ði ɪnˈstrʌkʃənz ˈpɜrfəktli.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was a perfectly clear night.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Era una noche perfectamente despejada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪt wʌz ə ˈpɜrfəktli klɪr naɪt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kwaɪt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm quite tired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estoy bastante cansado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪm kwaɪt ˈtaɪərd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The movie was quite interesting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La película fue bastante interesante.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈmuvi wʌz kwaɪt ˈɪntrəstɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He's quite good at soccer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él es bastante bueno en fútbol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hiz kwaɪt ɡʊd æt ˈsɑkər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's quite cold outside.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hace bastante frío afuera.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts kwaɪt koʊld ˈaʊtˈsaɪd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was quite upset about the news.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella estaba bastante molesta por la noticia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz kwaɪt əpˈsɛt əˈbaʊt ðə nuz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Más bien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈræðər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I would rather stay home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferiría quedarme en casa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ wʊd ˈræðər steɪ hoʊm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She found the movie rather boring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella encontró la película bastante aburrida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi faʊnd ðə ˈmuvi ˈræðər ˈbɔrɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was rather a difficult task.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fue una tarea bastante difícil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪt wʌz ˈræðər ə ˈdɪfəkəlt tæsk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He's rather tall for his age.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él es bastante alto para su edad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hiz ˈræðər tɔl fɔr hɪz eɪʤ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The results were rather unexpected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los resultados fueron bastante inesperados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə rɪˈzʌlts wɜr ˈræðər ˌʌnɪkˈspɛktɪd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Really</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realmente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈrɪli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I really like this song.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Me gusta mucho esta canción.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ ˈrɪli laɪk ðɪs sɔŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She really wants to win.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella realmente quiere ganar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˈrɪli wɑnts tu wɪn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They were really helpful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fueron de gran ayuda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ wɜr ˈrɪli ˈhɛlpfəl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He really needs to focus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él realmente necesita concentrarse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi ˈrɪli nidz tu ˈfoʊkəs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's really hot today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hace mucho calor hoy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈrɪli hɑt təˈdeɪ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarcely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈskɛrsli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I could scarcely believe it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas podía creerlo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ kʊd ˈskɛrsli bɪˈliv ɪt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She had scarcely finished when he arrived.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas había terminado cuando él llegó.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi hæd ˈskɛrsli ˈfɪnɪʃt wɛn hi əˈraɪvd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They scarcely speak to each other.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas se hablaban.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ ˈskɛrsli spik tu iʧ ˈʌðər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He had scarcely any money left.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apenas le quedaba dinero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi hæd ˈskɛrsli ˈɛni ˈmʌni lɛft.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The train had scarcely left the station.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El tren apenas había salido de la estación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə treɪn hæd ˈskɛrsli lɛft ðə ˈsteɪʃən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈsɪmpli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I simply love your dress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplemente me encanta tu vestido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ ˈsɪmpli lʌv jʊər drɛs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He simply ignored my advice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él simplemente ignoró mi consejo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi ˈsɪmpli ɪɡˈnɔrd maɪ ædˈvaɪs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She simply walked away.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella simplemente se alejó.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˈsɪmpli wɔkt əˈweɪ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We simply must get together soon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplemente debemos reunirnos pronto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi ˈsɪmpli mʌst ɡɛt təˈɡɛðər sun.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's simply not possible to finish on time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplemente no es posible terminar a tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈsɪmpli nɑt ˈpɑsəbəl tu ˈfɪnɪʃ ɑn taɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slightly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un poco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈslaɪtli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The milk tastes slightly sour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La leche sabe un poco agria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə mɪlk teɪsts ˈslaɪtli ˈsaʊər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She smiled slightly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella sonrió levemente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi smaɪld ˈslaɪtli.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The price is slightly higher than expected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El precio es un poco más alto de lo esperado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə praɪs ɪz ˈslaɪtli ˈhaɪər ðæn ɪkˈspɛktɪd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He's slightly taller than his brother.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él es un poco más alto que su hermano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hiz ˈslaɪtli ˈtɔlər ðæn hɪz ˈbrʌðər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The plan was slightly altered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El plan fue ligeramente modificado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə plæn wʌz ˈslaɪtli ˈɔltərd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entonces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soʊ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was so cold last night.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anoche hacía mucho frío.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪt wʌz soʊ koʊld læst naɪt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was so happy to see him.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella estaba tan feliz de verlo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz soʊ ˈhæpi tu si hɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The task was so difficult.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La tarea era tan difícil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə tæsk wʌz soʊ ˈdɪfəkəlt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They are so alike.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son tan parecidos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ ɑr soʊ əˈlaɪk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He drove so fast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él conducía tan rápido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi droʊv soʊ fæst.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strongly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totalmente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈstrɔŋli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She strongly disagrees with the decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella está totalmente en desacuerdo con la decisión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˈstrɔŋli dɪsəˈɡriz wɪð ðə dɪˈsɪʒən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I feel strongly about this issue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tengo una opinión muy firme sobre este tema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ fil ˈstrɔŋli əˈbaʊt ðɪs ˈɪʃu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He was strongly influenced by his mentor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él fue fuertemente influenciado por su mentor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi wʌz ˈstrɔŋli ˈɪnfluənst baɪ hɪz ˈmɛnˌtɔr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They are strongly committed to the project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Están muy comprometidos con el proyecto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ ɑr ˈstrɔŋli kəˈmɪtəd tu ðə ˈprɑʤɛkt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The door was strongly secured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La puerta estaba bien cerrada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə dɔr wʌz ˈstrɔŋli sɪˈkjʊrd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Too</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demasiado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's too hot to go outside.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hace demasiado calor para salir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts tu hɑt tu ɡoʊ ˈaʊtˈsaɪd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was too tired to continue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estaba demasiado cansada para continuar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz tu ˈtaɪərd tu kənˈtɪnju.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The suitcase is too heavy to lift.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maleta es demasiado pesada para levantarla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈsutˌkeɪs ɪz tu ˈhɛvi tu lɪft.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He's driving too fast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él está conduciendo demasiado rápido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hiz ˈdraɪvɪŋ tu fæst.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They arrived too late to see the beginning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llegaron demasiado tarde para ver el comienzo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ əˈraɪvd tu leɪt tu si ðə bɪˈɡɪnɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈʌtərli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was utterly amazed by the performance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Me sorprendió muchísimo la actuación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ wʌz ˈʌtərli əˈmeɪzd baɪ ðə pərˈfɔrməns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She felt utterly defeated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se sintió completamente derrotada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi fɛlt ˈʌtərli dɪˈfitɪd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The theory was utterly disproven.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La teoría quedó totalmente refutada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈθɪri wʌz ˈʌtərli dɪˈspruvɪn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He was utterly unaware of the situation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él no tenía ni idea de la situación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi wʌz ˈʌtərli ˌʌnəˈwɛr ʌv ðə ˌsɪʧuˈeɪʃən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The place was utterly deserted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El lugar estaba completamente desierto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə pleɪs wʌz ˈʌtərli dɪˈzɜrtɪd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈvɛri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm very interested in this book.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estoy muy interesado en este libro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪm ˈvɛri ˈɪntrɪstɪd ɪn ðɪs bʊk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was very pleased with the results.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estaba muy contenta con los resultados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi wʌz ˈvɛri plizd wɪð ðə rɪˈzʌlts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The coffee is very hot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El café está muy caliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈkɑfi ɪz ˈvɛri hɑt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He works very hard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él trabaja muy duro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi wɜrks ˈvɛri hɑrd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They were very quiet during the movie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estuvieron muy callados durante la película.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ wɜr ˈvɛri ˈkwaɪət ˈdʊrɪŋ ðə ˈmuvi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the meantime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mientras tanto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ðə ˈminˌtaɪm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the meantime, I'll prepare the documents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mientras tanto, prepararé los documentos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ðə ˈminˌtaɪm, aɪl priˈpɛr ðə ˈdɑkjəmənts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix yourself a snack; in the meantime, I'll finish up here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepárate un tentempié; mientras tanto, yo terminaré aquí.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fɪks jərˈsɛlf ə snæk; ɪn ðə ˈminˌtaɪm, aɪl ˈfɪnɪʃ ʌp hir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the meantime, can you check on the laundry?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mientras tanto, ¿puedes ir a ver cómo va la ropa?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ðə ˈminˌtaɪm, kæn ju ʧɛk ɑn ðə ˈlɔndri?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She's going to call us back soon; in the meantime, let's keep working.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nos llamará pronto; mientras tanto, sigamos trabajando.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃiz ˈɡoʊɪŋ tu kɔl ʌs bæk sun; ɪn ðə ˈminˌtaɪm, lɛts kip ˈwɜrkɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We'll hear the results tomorrow; in the meantime, let's not worry too much.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mañana nos darán los resultados; mientras tanto, no nos preocupemos demasiado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wil hir ðə rɪˈzʌlts təˈmɑˌroʊ; ɪn ðə ˈminˌtaɪm, lɛts nɑt ˈwɜri tu mʌʧ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once in a while</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De vez en cuando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wʌns ɪn ə waɪl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once in a while, we go out for Italian food.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De vez en cuando, salimos a comer comida italiana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wʌns ɪn ə waɪl, wi ɡoʊ aʊt fɔr ɪˈtæljən fud.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's good to disconnect from technology once in a while.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es bueno desconectarse de la tecnología de vez en cuando.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ɡʊd tu dɪskəˈnɛkt frʌm tɛkˈnɑləʤi wʌns ɪn ə waɪl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I still think of him once in a while.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todavía pienso en él de vez en cuando.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ stɪl θɪŋk ʌv hɪm wʌns ɪn ə waɪl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once in a while, a movie comes along that really makes you think.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De vez en cuando, aparece una película que te hace pensar de verdad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wʌns ɪn ə waɪl, ə ˈmuvi kʌmz əˈlɔŋ ðæt ˈrɪli meɪks ju θɪŋk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Try to treat yourself once in a while.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intenta darte un capricho de vez en cuando.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">traɪ tu trit jərˈsɛlf wʌns ɪn ə waɪl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under no circumstances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajo ninguna circunstancia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈʌndər noʊ ˈsɜrkəmˌstænsəz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under no circumstances should you open that door.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajo ninguna circunstancia debes abrir esa puerta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈʌndər noʊ ˈsɜrkəmˌstænsəz ʃʊd ju ˈoʊpən ðæt dɔr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He must be watched under no circumstances.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajo ninguna circunstancia hay que vigilarlo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi mʌst bi wɑʧt ˈʌndər noʊ ˈsɜrkəmˌstænsəz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under no circumstances can we accept late submissions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajo ninguna circunstancia podemos aceptar entregas fuera de plazo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈʌndər noʊ ˈsɜrkəmˌstænsəz kæn wi ækˈsɛpt leɪt səbˈmɪʃənz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You should under no circumstances ignore this warning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajo ninguna circunstancia debes ignorar esta advertencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ju ʃʊd ˈʌndər noʊ ˈsɜrkəmˌstænsəz ɪɡˈnɔr ðɪs ˈwɔrnɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under no circumstances will I agree to those terms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajo ninguna circunstancia aceptaré esos términos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈʌndər noʊ ˈsɜrkəmˌstænsəz wɪl aɪ əˈɡri tu ðoʊz tɜrmz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the long run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A largo plazo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ðə lɔŋ rʌn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eating healthy pays off in the long run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comer sano da sus frutos a largo plazo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈitɪŋ ˈhɛlθi peɪz ɔf ɪn ðə lɔŋ rʌn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These repairs will be more economical in the long run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estas reparaciones serán más económicas a largo plazo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðiz rɪˈpɛrz wɪl bi mɔr ˌɛkəˈnɑmɪkəl ɪn ðə lɔŋ rʌn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's a big investment, but it will benefit us in the long run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es una gran inversión, pero nos beneficiará a largo plazo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ə bɪɡ ɪnˈvɛstmənt, bʌt ɪt wɪl ˈbɛnəfɪt ʌs ɪn ðə lɔŋ rʌn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studying hard will make your future easier in the long run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estudiar mucho hará que tu futuro sea más fácil a largo plazo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈstʌdiɪŋ hɑrd wɪl meɪk jʊər ˈfjuʧər ˈiziər ɪn ðə lɔŋ rʌn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the long run, patience yields better results.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A largo plazo, la paciencia produce mejores resultados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ðə lɔŋ rʌn, ˈpeɪʃəns jildz ˈbɛtər rɪˈzʌlts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By all means</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por supuesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baɪ ɔl minz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you think it will help, by all means, go ahead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si crees que ayudará, por supuesto, sigue adelante.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪf ju θɪŋk ɪt wɪl hɛlp, baɪ ɔl minz, ɡoʊ əˈhɛd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please, by all means, take a seat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por favor, por supuesto, toma asiento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pliz, baɪ ɔl minz, teɪk ə sit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By all means, let's start the meeting without them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por supuesto, empecemos la reunión sin ellos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baɪ ɔl minz, lɛts stɑrt ðə ˈmitɪŋ wɪˈθaʊt ðɛm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call me later if you need to talk, by all means.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llámame más tarde si necesitas hablar, por supuesto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kɔl mi ˈleɪtər ɪf ju nid tu tɔk, baɪ ɔl minz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By all means, choose the color you like best.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por supuesto, elige el color que más te guste.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baɪ ɔl minz, ʧuz ðə ˈkʌlər ju laɪk bɛst.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At all costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A toda costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt ɔl kɑsts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We must protect the environment at all costs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debemos proteger el medio ambiente a toda costa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi mʌst prəˈtɛkt ði ɪnˈvaɪrənmənt æt ɔl kɑsts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep the secret at all costs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guarda el secreto a toda costa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kip ðə ˈsikrət æt ɔl kɑsts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At all costs, avoid any discussions about politics at dinner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A toda costa, evita cualquier discusión sobre política en la cena.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt ɔl kɑsts, əˈvɔɪd ˈɛni dɪˈskʌʃənz əˈbaʊt ˈpɑləˌtɪks æt ˈdɪnər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He plans to win at all costs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planea ganar a toda costa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi plænz tu wɪn æt ɔl kɑsts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We have to secure the data at all costs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenemos que asegurar los datos a toda costa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi hæv tu sɪˈkjʊr ðə ˈdeɪtə æt ɔl kɑsts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In vain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En vano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn veɪn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He tried to apologize, but it was in vain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intentó disculparse, pero fue en vano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi traɪd tu əˈpɑləˌʤaɪz, bʌt ɪt wʌz ɪn veɪn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All their efforts to save the tree were in vain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos sus esfuerzos por salvar el árbol fueron en vano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɔl ðɛr ˈɛfərts tu seɪv ðə tri wɜr ɪn veɪn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She waited in vain for a reply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esperó en vano una respuesta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˈweɪtɪd ɪn veɪn fɔr ə rɪˈplaɪ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They attempted to reach the summit, but it was in vain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intentaron llegar a la cima, pero fue en vano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ əˈtɛmptəd tu riʧ ðə ˈsʌmət, bʌt ɪt wʌz ɪn veɪn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't let your hard work be in vain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No dejes que tu arduo trabajo sea en vano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doʊnt lɛt jʊər hɑrd wɜrk bi ɪn veɪn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En promedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɑn ˈævərɪʤ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On average, people check their phones 150 times a day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En promedio, la gente revisa sus teléfonos 150 veces al día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɑn ˈævərɪʤ, ˈpipəl ʧɛk ðɛr foʊnz 150 taɪmz ə deɪ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She sleeps on average eight hours a night.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duerme en promedio ocho horas por noche.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi slips ɑn ˈævərɪʤ eɪt ˈaʊərz ə naɪt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On average, how much do you spend on groceries?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En promedio, ¿cuánto gastas en comestibles?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɑn ˈævərɪʤ, haʊ mʌʧ du ju spɛnd ɑn ˈɡroʊsəriz?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The temperature is, on average, higher this summer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La temperatura es, en promedio, más alta este verano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈtɛmprəʧər ɪz, ɑn ˈævərɪʤ, ˈhaɪər ðɪs ˈsʌmər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On average, our customers save about 10%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En promedio, nuestros clientes ahorran alrededor del 10%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɑn ˈævərɪʤ, ˈaʊər ˈkʌstəmərz seɪv əˈbaʊt 10%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At a glance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De un vistazo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt ə ɡlæns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I could tell at a glance that something was wrong.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pude darme cuenta de que algo andaba mal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ kʊd tɛl æt ə ɡlæns ðæt ˈsʌmθɪŋ wʌz rɔŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He knew at a glance she was angry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabía de un vistazo que estaba enojada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi nu æt ə ɡlæns ʃi wʌz ˈæŋɡri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At a glance, the answer seemed obvious.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De un vistazo, la respuesta parecía obvia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt ə ɡlæns, ði ˈænsər simd ˈɑbviəs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can see the quality of the fabric at a glance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se puede ver la calidad de la tela de un vistazo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ju kæn si ðə ˈkwɑləti ʌv ðə ˈfæbrɪk æt ə ɡlæns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She caught the mistake at a glance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella detectó el error de un vistazo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi kɑt ðə mɪsˈteɪk æt ə ɡlæns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beyond doubt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin duda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bɪˈɑnd daʊt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">His loyalty is beyond doubt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Su lealtad está fuera de toda duda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hɪz ˈlɔɪəlti ɪz bɪˈɑnd daʊt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The success of the project is now beyond doubt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El éxito del proyecto ahora está fuera de toda duda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə səkˈsɛs ʌv ðə ˈprɑʤɛkt ɪz naʊ bɪˈɑnd daʊt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This evidence puts her innocence beyond doubt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esta evidencia pone su inocencia fuera de toda duda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðɪs ˈɛvədəns pʊts hɜr ˈɪnəsəns bɪˈɑnd daʊt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">His expertise in the subject is beyond doubt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Su experiencia en el tema está fuera de toda duda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hɪz ˌɛkspərˈtiz ɪn ðə ˈsʌbʤɪkt ɪz bɪˈɑnd daʊt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The benefits of exercise are beyond doubt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los beneficios del ejercicio están fuera de toda duda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈbɛnəfɪts ʌv ˈɛksərˌsaɪz ɑr bɪˈɑnd daʊt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En primer lugar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt fɜrst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At first, I was nervous about the presentation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al principio, estaba nervioso por la presentación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt fɜrst, aɪ wʌz ˈnɜrvəs əˈbaʊt ðə ˌprɛzənˈteɪʃən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At first, the instructions seemed complicated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al principio, las instrucciones parecían complicadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt fɜrst, ði ɪnˈstrʌkʃənz simd ˈkɑmpləˌkeɪtəd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At first, he didn’t recognize me.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al principio, no me reconoció.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt fɜrst, hi ˈdɪdənt ˈrɛkəɡˌnaɪz mi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At first, the task appeared easy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al principio, la tarea parecía fácil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt fɜrst, ðə tæsk əˈpɪrd ˈizi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At first, we took the wrong road.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al principio, tomamos el camino equivocado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt fɜrst, wi tʊk ðə rɔŋ roʊd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por casualidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baɪ ʧæns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I found this book by chance in an old bookstore.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encontré este libro por casualidad en una librería vieja.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ faʊnd ðɪs bʊk baɪ ʧæns ɪn ən oʊld ˈbʊkˌstɔr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We ended up at the same cafe by chance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminamos en el mismo café por casualidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi ˈɛndɪd ʌp æt ðə seɪm kəˈfeɪ baɪ ʧæns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By chance, I overheard their conversation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por casualidad, escuché su conversación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baɪ ʧæns, aɪ ˈoʊvərˈhɜrd ðɛr ˌkɑnvərˈseɪʃən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She bumped into her old friend by chance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se topó con su vieja amiga por casualidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi bʌmpt ˈɪntu hɜr oʊld frɛnd baɪ ʧæns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By chance, I discovered a new route home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por casualidad, descubrí una nueva ruta a casa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baɪ ʧæns, aɪ dɪˈskʌvərd ə nu rut hoʊm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In addition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Además</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn əˈdɪʃən</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In addition, we will need more time to finish.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Además, necesitaremos más tiempo para terminar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn əˈdɪʃən, wi wɪl nid mɔr taɪm tu ˈfɪnɪʃ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In addition, she mentioned some changes to the plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Además, mencionó algunos cambios en el plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn əˈdɪʃən, ʃi ˈmɛnʃənd sʌm ˈʧeɪnʤəz tu ðə plæn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In addition, four more people will join us.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Además, se unirán cuatro personas más.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn əˈdɪʃən, fɔr mɔr ˈpipəl wɪl ʤɔɪn ʌs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In addition to the main course, we have two sides.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Además del plato principal, tenemos dos guarniciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn əˈdɪʃən tu ðə meɪn kɔrs, wi hæv tu saɪdz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In addition, I'd like to thank everyone for coming.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Además, me gustaría agradecerles a todos por venir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn əˈdɪʃən, aɪd laɪk tu θæŋk ˈɛvriˌwʌn fɔr ˈkʌmɪŋ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A propósito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɑn ˈpɜrpəs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He missed the meeting on purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él faltó a la reunión a propósito.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi mɪst ðə ˈmitɪŋ ɑn ˈpɜrpəs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She dropped the hint on purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella soltó la indirecta a propósito.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi drɑpt ðə hɪnt ɑn ˈpɜrpəs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I left early on purpose to avoid traffic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Me fui temprano a propósito para evitar el tráfico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪ lɛft ˈɜrli ɑn ˈpɜrpəs tu əˈvɔɪd ˈtræfɪk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He ignored my call on purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él ignoró mi llamada a propósito.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi ɪɡˈnɔrd maɪ kɔl ɑn ˈpɜrpəs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She made a loud noise on purpose to get attention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella hizo un ruido fuerte a propósito para llamar la atención.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi meɪd ə laʊd nɔɪz ɑn ˈpɜrpəs tu ɡɛt əˈtɛnʃən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para siempre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fɔr ɡʊd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He has left the job for good.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dejó el trabajo para siempre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi hæz lɛft ðə ʤɑb fɔr ɡʊd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She decided to move to Canada for good.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella decidió mudarse a Canadá para siempre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˌdɪˈsaɪdɪd tu muv tu ˈkænədə fɔr ɡʊd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They closed the store for good.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerraron la tienda para siempre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ kloʊzd ðə stɔr fɔr ɡʊd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I've given up fast food for good.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dejé la comida rápida para siempre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aɪv ˈɡɪvən ʌp fæst fud fɔr ɡʊd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He’s fixing the machine for good this time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esta vez está arreglando la máquina para siempre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hiz ˈfɪksɪŋ ðə məˈʃin fɔr ɡʊd ðɪs taɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At least</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al menos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At least try to be on time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al menos intenta llegar a tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt list traɪ tu bi ɑn taɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She could at least have called.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al menos podría haber llamado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi kʊd æt list hæv kɔld.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We should at least check the weather.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al menos deberíamos consultar el clima.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi ʃʊd æt list ʧɛk ðə ˈwɛðər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At least the day ended well.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al menos el día terminó bien.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt list ðə deɪ ˈɛndɪd wɛl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He could eat at least some of the meal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudo comer al menos algo de la comida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi kʊd it æt list sʌm ʌv ðə mil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In general</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En general</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ˈʤɛnərəl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In general, the results are positive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En general, los resultados son positivos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ˈʤɛnərəl, ðə rɪˈzʌlts ɑr ˈpɑzətɪv.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In general, winters are mild here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En general, los inviernos son suaves aquí.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ˈʤɛnərəl, ˈwɪntərz ɑr maɪld hir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People, in general, like to feel appreciated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A la gente, en general, le gusta sentirse apreciada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈpipəl, ɪn ˈʤɛnərəl, laɪk tu fil əˈpriʃiˌeɪtɪd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In general, the software performs well.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En general, el software funciona bien.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ˈʤɛnərəl, ðə ˈsɔfˌtwɛr pərˈfɔrmz wɛl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In general, the plan seems sound.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En general, el plan parece sólido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ˈʤɛnərəl, ðə plæn simz saʊnd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out of nowhere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De la nada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aʊt ʌv ˈnoʊˌwɛr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A deer ran out of nowhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un ciervo salió corriendo de la nada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə dɪr ræn aʊt ʌv ˈnoʊˌwɛr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The idea came to me out of nowhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La idea se me ocurrió de la nada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ði aɪˈdiə keɪm tu mi aʊt ʌv ˈnoʊˌwɛr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out of nowhere, a loud sound startled us.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De la nada, un sonido fuerte nos sobresaltó.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aʊt ʌv ˈnoʊˌwɛr, ə laʊd saʊnd ˈstɑrtəld ʌs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He appeared out of nowhere in the hallway.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apareció de la nada en el pasillo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi əˈpɪrd aʊt ʌv ˈnoʊˌwɛr ɪn ðə ˈhɔlˌweɪ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out of nowhere, she asked a very personal question.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De la nada, ella hizo una pregunta muy personal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aʊt ʌv ˈnoʊˌwɛr, ʃi æskt ə ˈvɛri ˈpɜrsɪnɪl ˈkwɛsʧən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A tiempo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɑn taɪm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The train arrived on time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El tren llegó a tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə treɪn əˈraɪvd ɑn taɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make sure you’re on time for the interview.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asegúrate de llegar a tiempo a la entrevista.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meɪk ʃʊr jʊr ɑn taɪm fɔr ði ˈɪntərˌvju.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He prides himself on being on time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él se enorgullece de ser puntual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi praɪdz hɪmˈsɛlf ɑn ˈbiɪŋ ɑn taɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The project was completed on time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El proyecto se completó a tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə ˈprɑʤɛkt wʌz kəmˈplitɪd ɑn taɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She always submits her assignments on time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella siempre entrega sus tareas a tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃi ˈɔlˌweɪz ˌsʌbˈmɪts hɜr əˈsaɪnmənts ɑn taɪm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All of a sudden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De repente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɔl ʌv ə ˈsʌdən</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All of a sudden, the lights went out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De repente, las luces se apagaron.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɔl ʌv ə ˈsʌdən, ðə laɪts wɛnt aʊt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All of a sudden, she felt dizzy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De repente, se sintió mareada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɔl ʌv ə ˈsʌdən, ʃi fɛlt ˈdɪzi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The car stopped all of a sudden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El auto se detuvo de repente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðə kɑr stɑpt ɔl ʌv ə ˈsʌdən.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All of a sudden, the room went quiet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De repente, la habitación quedó en silencio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɔl ʌv ə ˈsʌdən, ðə rum wɛnt ˈkwaɪət.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He stood up all of a sudden and left.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De repente, él se levantó y se fue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi stʊd ʌp ɔl ʌv ə ˈsʌdən ænd lɛft.</t>
   </si>
 </sst>
 </file>
@@ -5048,7 +7408,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.02"/>
@@ -6292,241 +8652,6 @@
         <v>571</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="F107" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -6556,24 +8681,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>596</v>
+        <v>545</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>597</v>
+        <v>546</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>598</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>599</v>
+        <v>548</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>600</v>
+        <v>549</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>601</v>
+        <v>550</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>6</v>
@@ -6581,13 +8706,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>602</v>
+        <v>551</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>603</v>
+        <v>552</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>604</v>
+        <v>553</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
@@ -6595,13 +8720,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>605</v>
+        <v>554</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>606</v>
+        <v>555</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>607</v>
+        <v>556</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
@@ -6609,13 +8734,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>608</v>
+        <v>557</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>609</v>
+        <v>558</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>610</v>
+        <v>559</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
@@ -6623,13 +8748,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>611</v>
+        <v>560</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>612</v>
+        <v>561</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>613</v>
+        <v>562</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
@@ -6637,13 +8762,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>614</v>
+        <v>563</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>615</v>
+        <v>564</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>616</v>
+        <v>565</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -6651,13 +8776,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>617</v>
+        <v>566</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>618</v>
+        <v>567</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -6665,13 +8790,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>620</v>
+        <v>569</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>621</v>
+        <v>570</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>622</v>
+        <v>571</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
@@ -6679,13 +8804,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>623</v>
+        <v>572</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>624</v>
+        <v>573</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>625</v>
+        <v>574</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
@@ -6693,13 +8818,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>626</v>
+        <v>575</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>627</v>
+        <v>576</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>628</v>
+        <v>577</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
@@ -6707,13 +8832,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>629</v>
+        <v>578</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>630</v>
+        <v>579</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>631</v>
+        <v>580</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -6721,13 +8846,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>632</v>
+        <v>581</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>634</v>
+        <v>583</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>6</v>
@@ -6735,13 +8860,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>635</v>
+        <v>584</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>637</v>
+        <v>586</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -6749,13 +8874,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>638</v>
+        <v>587</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>639</v>
+        <v>588</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>640</v>
+        <v>589</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
@@ -6763,13 +8888,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>641</v>
+        <v>590</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>642</v>
+        <v>591</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>643</v>
+        <v>592</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
@@ -6777,13 +8902,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>644</v>
+        <v>593</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>645</v>
+        <v>594</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>646</v>
+        <v>595</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
@@ -6791,13 +8916,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>647</v>
+        <v>596</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>648</v>
+        <v>597</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>649</v>
+        <v>598</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
@@ -6805,13 +8930,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>650</v>
+        <v>599</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>651</v>
+        <v>600</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>652</v>
+        <v>601</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -6819,24 +8944,24 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>653</v>
+        <v>602</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>654</v>
+        <v>603</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>655</v>
+        <v>604</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>656</v>
+        <v>605</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>657</v>
+        <v>606</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>658</v>
+        <v>607</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -6844,13 +8969,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>659</v>
+        <v>608</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>660</v>
+        <v>609</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>661</v>
+        <v>610</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>6</v>
@@ -6858,13 +8983,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>662</v>
+        <v>611</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>663</v>
+        <v>612</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>664</v>
+        <v>613</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -6872,13 +8997,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>665</v>
+        <v>614</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>666</v>
+        <v>615</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>667</v>
+        <v>616</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -6886,13 +9011,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>668</v>
+        <v>617</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>669</v>
+        <v>618</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>670</v>
+        <v>619</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
@@ -6900,13 +9025,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>671</v>
+        <v>620</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>672</v>
+        <v>621</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>673</v>
+        <v>622</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>6</v>
@@ -6914,13 +9039,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>674</v>
+        <v>623</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>675</v>
+        <v>624</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>676</v>
+        <v>625</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>6</v>
@@ -6928,13 +9053,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>677</v>
+        <v>626</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>678</v>
+        <v>627</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>679</v>
+        <v>628</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>6</v>
@@ -6942,13 +9067,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>680</v>
+        <v>629</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>681</v>
+        <v>630</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>682</v>
+        <v>631</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>6</v>
@@ -6956,13 +9081,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>683</v>
+        <v>632</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>684</v>
+        <v>633</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>685</v>
+        <v>634</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>6</v>
@@ -6970,13 +9095,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>686</v>
+        <v>635</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>687</v>
+        <v>636</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>688</v>
+        <v>637</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>6</v>
@@ -6984,13 +9109,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>689</v>
+        <v>638</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>690</v>
+        <v>639</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>691</v>
+        <v>640</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>6</v>
@@ -6998,13 +9123,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>692</v>
+        <v>641</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>693</v>
+        <v>642</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>694</v>
+        <v>643</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>6</v>
@@ -7012,13 +9137,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>695</v>
+        <v>644</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>696</v>
+        <v>645</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>697</v>
+        <v>646</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>6</v>
@@ -7026,13 +9151,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>698</v>
+        <v>647</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>699</v>
+        <v>648</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>700</v>
+        <v>649</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>6</v>
@@ -7040,13 +9165,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>701</v>
+        <v>650</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>702</v>
+        <v>651</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>703</v>
+        <v>652</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -7054,13 +9179,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>704</v>
+        <v>653</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>705</v>
+        <v>654</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>706</v>
+        <v>655</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -7068,13 +9193,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>707</v>
+        <v>656</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>708</v>
+        <v>657</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>709</v>
+        <v>658</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -7082,13 +9207,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>710</v>
+        <v>659</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>711</v>
+        <v>660</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>712</v>
+        <v>661</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -7096,24 +9221,24 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>713</v>
+        <v>662</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>714</v>
+        <v>663</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>715</v>
+        <v>664</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>716</v>
+        <v>665</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>717</v>
+        <v>666</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>718</v>
+        <v>667</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -7121,13 +9246,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>719</v>
+        <v>668</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>720</v>
+        <v>669</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>721</v>
+        <v>670</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -7135,13 +9260,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>722</v>
+        <v>671</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>723</v>
+        <v>672</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>724</v>
+        <v>673</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -7149,13 +9274,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>725</v>
+        <v>674</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>726</v>
+        <v>675</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>727</v>
+        <v>676</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -7163,13 +9288,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>728</v>
+        <v>677</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>729</v>
+        <v>678</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>730</v>
+        <v>679</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -7177,13 +9302,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>731</v>
+        <v>680</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>732</v>
+        <v>681</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>733</v>
+        <v>682</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -7191,13 +9316,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>734</v>
+        <v>683</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>735</v>
+        <v>684</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>736</v>
+        <v>685</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -7205,13 +9330,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>737</v>
+        <v>686</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>738</v>
+        <v>687</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>739</v>
+        <v>688</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -7219,13 +9344,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>740</v>
+        <v>689</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>741</v>
+        <v>690</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>742</v>
+        <v>691</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -7233,13 +9358,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>743</v>
+        <v>692</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>744</v>
+        <v>693</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>745</v>
+        <v>694</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -7247,13 +9372,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>746</v>
+        <v>695</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>747</v>
+        <v>696</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>748</v>
+        <v>697</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -7261,13 +9386,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>749</v>
+        <v>698</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>750</v>
+        <v>699</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>751</v>
+        <v>700</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -7275,13 +9400,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>752</v>
+        <v>701</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>753</v>
+        <v>702</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>754</v>
+        <v>703</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -7289,13 +9414,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>755</v>
+        <v>704</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>756</v>
+        <v>705</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>757</v>
+        <v>706</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -7303,13 +9428,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>758</v>
+        <v>707</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>759</v>
+        <v>708</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>760</v>
+        <v>709</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -7317,13 +9442,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>761</v>
+        <v>710</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>762</v>
+        <v>711</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>763</v>
+        <v>712</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -7331,13 +9456,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>764</v>
+        <v>713</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>765</v>
+        <v>714</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>766</v>
+        <v>715</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -7345,13 +9470,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>767</v>
+        <v>716</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>768</v>
+        <v>717</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>769</v>
+        <v>718</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -7359,24 +9484,24 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>770</v>
+        <v>719</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>771</v>
+        <v>720</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>772</v>
+        <v>721</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>773</v>
+        <v>722</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>774</v>
+        <v>723</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>775</v>
+        <v>724</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -7384,13 +9509,13 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>776</v>
+        <v>725</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>777</v>
+        <v>726</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>778</v>
+        <v>727</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -7398,13 +9523,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>779</v>
+        <v>728</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>780</v>
+        <v>729</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>781</v>
+        <v>730</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -7412,13 +9537,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>782</v>
+        <v>731</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>783</v>
+        <v>732</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>784</v>
+        <v>733</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -7426,13 +9551,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>785</v>
+        <v>734</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>786</v>
+        <v>735</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>787</v>
+        <v>736</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -7440,13 +9565,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>788</v>
+        <v>737</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>789</v>
+        <v>738</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>790</v>
+        <v>739</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -7454,13 +9579,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>791</v>
+        <v>740</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>792</v>
+        <v>741</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>793</v>
+        <v>742</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -7468,13 +9593,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>794</v>
+        <v>743</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>795</v>
+        <v>744</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>796</v>
+        <v>745</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -7482,13 +9607,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>797</v>
+        <v>746</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>798</v>
+        <v>747</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>799</v>
+        <v>748</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -7496,13 +9621,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>800</v>
+        <v>749</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>801</v>
+        <v>750</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>802</v>
+        <v>751</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -7510,13 +9635,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>803</v>
+        <v>752</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>804</v>
+        <v>753</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>805</v>
+        <v>754</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -7524,13 +9649,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>806</v>
+        <v>755</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>807</v>
+        <v>756</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>808</v>
+        <v>757</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -7538,13 +9663,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>809</v>
+        <v>758</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>810</v>
+        <v>759</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>811</v>
+        <v>760</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -7552,13 +9677,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>812</v>
+        <v>761</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>813</v>
+        <v>762</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>814</v>
+        <v>763</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -7566,13 +9691,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>815</v>
+        <v>764</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>816</v>
+        <v>765</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>817</v>
+        <v>766</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>6</v>
@@ -7580,13 +9705,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>818</v>
+        <v>767</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>819</v>
+        <v>768</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>820</v>
+        <v>769</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>6</v>
@@ -7594,13 +9719,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>821</v>
+        <v>770</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>822</v>
+        <v>771</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>823</v>
+        <v>772</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>6</v>
@@ -7608,13 +9733,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>824</v>
+        <v>773</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>825</v>
+        <v>774</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>826</v>
+        <v>775</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>6</v>
@@ -7622,24 +9747,24 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>827</v>
+        <v>776</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>828</v>
+        <v>777</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>829</v>
+        <v>778</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>830</v>
+        <v>779</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>831</v>
+        <v>780</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>832</v>
+        <v>781</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>6</v>
@@ -7647,13 +9772,13 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>833</v>
+        <v>782</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>833</v>
+        <v>782</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>834</v>
+        <v>783</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>6</v>
@@ -7661,13 +9786,13 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>835</v>
+        <v>784</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>836</v>
+        <v>785</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>837</v>
+        <v>786</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>6</v>
@@ -7675,13 +9800,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>838</v>
+        <v>787</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>839</v>
+        <v>788</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>840</v>
+        <v>789</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>6</v>
@@ -7689,13 +9814,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>841</v>
+        <v>790</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>842</v>
+        <v>791</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>843</v>
+        <v>792</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>6</v>
@@ -7703,13 +9828,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>844</v>
+        <v>793</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>845</v>
+        <v>794</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>846</v>
+        <v>795</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>6</v>
@@ -7717,13 +9842,13 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>847</v>
+        <v>796</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>848</v>
+        <v>797</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>849</v>
+        <v>798</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>6</v>
@@ -7731,13 +9856,13 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>850</v>
+        <v>799</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>851</v>
+        <v>800</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>852</v>
+        <v>801</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>6</v>
@@ -7745,13 +9870,13 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>853</v>
+        <v>802</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>854</v>
+        <v>803</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>855</v>
+        <v>804</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -7759,13 +9884,13 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>856</v>
+        <v>805</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>857</v>
+        <v>806</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>858</v>
+        <v>807</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>6</v>
@@ -7773,13 +9898,13 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>859</v>
+        <v>808</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>860</v>
+        <v>809</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>861</v>
+        <v>810</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>6</v>
@@ -7787,13 +9912,13 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>862</v>
+        <v>811</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>863</v>
+        <v>812</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>864</v>
+        <v>813</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -7801,13 +9926,13 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>865</v>
+        <v>814</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>866</v>
+        <v>815</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>867</v>
+        <v>816</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -7815,13 +9940,13 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>868</v>
+        <v>817</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>869</v>
+        <v>818</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>870</v>
+        <v>819</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -7829,13 +9954,13 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>871</v>
+        <v>820</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>872</v>
+        <v>821</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>873</v>
+        <v>822</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -7843,13 +9968,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>874</v>
+        <v>823</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>874</v>
+        <v>823</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>875</v>
+        <v>824</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -7857,13 +9982,13 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>876</v>
+        <v>825</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>877</v>
+        <v>826</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>878</v>
+        <v>827</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -7871,13 +9996,13 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>879</v>
+        <v>828</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>880</v>
+        <v>829</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>881</v>
+        <v>830</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>6</v>
@@ -7885,13 +10010,13 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>882</v>
+        <v>831</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>883</v>
+        <v>832</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>884</v>
+        <v>833</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>6</v>
@@ -7923,24 +10048,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>885</v>
+        <v>834</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>886</v>
+        <v>835</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>887</v>
+        <v>836</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>888</v>
+        <v>837</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>889</v>
+        <v>838</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>890</v>
+        <v>839</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>6</v>
@@ -7948,13 +10073,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>891</v>
+        <v>840</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>892</v>
+        <v>841</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>893</v>
+        <v>842</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
@@ -7962,13 +10087,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>894</v>
+        <v>843</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>895</v>
+        <v>844</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>896</v>
+        <v>845</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
@@ -7976,13 +10101,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>897</v>
+        <v>846</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>898</v>
+        <v>847</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>899</v>
+        <v>848</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
@@ -7990,13 +10115,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>900</v>
+        <v>849</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>901</v>
+        <v>850</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>902</v>
+        <v>851</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
@@ -8004,13 +10129,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>903</v>
+        <v>852</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>904</v>
+        <v>853</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>905</v>
+        <v>854</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -8018,13 +10143,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>906</v>
+        <v>855</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>907</v>
+        <v>856</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>908</v>
+        <v>857</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -8032,13 +10157,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>909</v>
+        <v>858</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>910</v>
+        <v>859</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>911</v>
+        <v>860</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
@@ -8046,13 +10171,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>912</v>
+        <v>861</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>913</v>
+        <v>862</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>914</v>
+        <v>863</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
@@ -8060,13 +10185,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>915</v>
+        <v>864</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>916</v>
+        <v>865</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>917</v>
+        <v>866</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
@@ -8074,13 +10199,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>918</v>
+        <v>867</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>919</v>
+        <v>868</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>920</v>
+        <v>869</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -8088,13 +10213,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>921</v>
+        <v>870</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>922</v>
+        <v>871</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>923</v>
+        <v>872</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>6</v>
@@ -8102,24 +10227,24 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>924</v>
+        <v>873</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>925</v>
+        <v>874</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>926</v>
+        <v>875</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>927</v>
+        <v>876</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>928</v>
+        <v>877</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>929</v>
+        <v>878</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
@@ -8127,13 +10252,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>930</v>
+        <v>879</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>931</v>
+        <v>880</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>932</v>
+        <v>881</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
@@ -8141,13 +10266,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>933</v>
+        <v>882</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>934</v>
+        <v>883</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>935</v>
+        <v>884</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
@@ -8155,13 +10280,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>936</v>
+        <v>885</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>937</v>
+        <v>886</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>938</v>
+        <v>887</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
@@ -8169,13 +10294,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>939</v>
+        <v>888</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>940</v>
+        <v>889</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>941</v>
+        <v>890</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -8183,13 +10308,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>942</v>
+        <v>891</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>943</v>
+        <v>892</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>944</v>
+        <v>893</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>6</v>
@@ -8197,13 +10322,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>945</v>
+        <v>894</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>946</v>
+        <v>895</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>947</v>
+        <v>896</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -8211,13 +10336,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>948</v>
+        <v>897</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>949</v>
+        <v>898</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>950</v>
+        <v>899</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>6</v>
@@ -8225,13 +10350,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>951</v>
+        <v>900</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>952</v>
+        <v>901</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>953</v>
+        <v>902</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -8239,13 +10364,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>954</v>
+        <v>903</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>955</v>
+        <v>904</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>956</v>
+        <v>905</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -8253,13 +10378,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>957</v>
+        <v>906</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>958</v>
+        <v>907</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>959</v>
+        <v>908</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
@@ -8267,13 +10392,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>960</v>
+        <v>909</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>961</v>
+        <v>910</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>962</v>
+        <v>911</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>6</v>
@@ -8281,13 +10406,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>963</v>
+        <v>912</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>964</v>
+        <v>913</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>965</v>
+        <v>914</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>6</v>
@@ -8319,25 +10444,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>966</v>
+        <v>915</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>967</v>
+        <v>916</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>968</v>
+        <v>917</v>
       </c>
       <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>969</v>
+        <v>918</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>970</v>
+        <v>919</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>971</v>
+        <v>920</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>6</v>
@@ -8345,13 +10470,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>972</v>
+        <v>921</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>973</v>
+        <v>922</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>974</v>
+        <v>923</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
@@ -8359,13 +10484,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>975</v>
+        <v>924</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>976</v>
+        <v>925</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>977</v>
+        <v>926</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
@@ -8373,13 +10498,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>978</v>
+        <v>927</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>979</v>
+        <v>928</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>980</v>
+        <v>929</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
@@ -8387,13 +10512,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>981</v>
+        <v>930</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>982</v>
+        <v>931</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>983</v>
+        <v>932</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
@@ -8401,13 +10526,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>984</v>
+        <v>933</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>985</v>
+        <v>934</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>986</v>
+        <v>935</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -8415,13 +10540,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>987</v>
+        <v>936</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>988</v>
+        <v>937</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>989</v>
+        <v>938</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -8429,13 +10554,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>990</v>
+        <v>939</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>991</v>
+        <v>940</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>992</v>
+        <v>941</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
@@ -8443,13 +10568,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>993</v>
+        <v>942</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>994</v>
+        <v>943</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>995</v>
+        <v>944</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
@@ -8457,13 +10582,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>996</v>
+        <v>945</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>997</v>
+        <v>946</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>998</v>
+        <v>947</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
@@ -8471,13 +10596,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>999</v>
+        <v>948</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1000</v>
+        <v>949</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1001</v>
+        <v>950</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -8485,13 +10610,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1002</v>
+        <v>951</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1003</v>
+        <v>952</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1004</v>
+        <v>953</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>6</v>
@@ -8499,13 +10624,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1005</v>
+        <v>954</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1006</v>
+        <v>955</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1007</v>
+        <v>956</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -8513,13 +10638,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1008</v>
+        <v>957</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1009</v>
+        <v>958</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1010</v>
+        <v>959</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
@@ -8527,13 +10652,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1011</v>
+        <v>960</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1012</v>
+        <v>961</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1013</v>
+        <v>962</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
@@ -8541,13 +10666,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1014</v>
+        <v>963</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1015</v>
+        <v>964</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1016</v>
+        <v>965</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
@@ -8555,13 +10680,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1017</v>
+        <v>966</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1018</v>
+        <v>967</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1019</v>
+        <v>968</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
@@ -8569,13 +10694,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1020</v>
+        <v>969</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1021</v>
+        <v>970</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1022</v>
+        <v>971</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -8583,13 +10708,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1023</v>
+        <v>972</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1024</v>
+        <v>973</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1025</v>
+        <v>974</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>6</v>
@@ -8597,13 +10722,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1026</v>
+        <v>975</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1027</v>
+        <v>976</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1028</v>
+        <v>977</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -8611,13 +10736,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1029</v>
+        <v>978</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1030</v>
+        <v>979</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1031</v>
+        <v>980</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>6</v>
@@ -8625,13 +10750,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1032</v>
+        <v>981</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1033</v>
+        <v>982</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1034</v>
+        <v>983</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -8639,13 +10764,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1035</v>
+        <v>984</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1036</v>
+        <v>985</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1037</v>
+        <v>986</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -8653,13 +10778,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1038</v>
+        <v>987</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1039</v>
+        <v>988</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1040</v>
+        <v>989</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
@@ -8667,13 +10792,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1041</v>
+        <v>990</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1042</v>
+        <v>991</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1043</v>
+        <v>992</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>6</v>
@@ -8681,25 +10806,25 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1044</v>
+        <v>993</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1045</v>
+        <v>994</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1046</v>
+        <v>995</v>
       </c>
       <c r="F27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1047</v>
+        <v>996</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1048</v>
+        <v>997</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1049</v>
+        <v>998</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>6</v>
@@ -8707,13 +10832,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1050</v>
+        <v>999</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1051</v>
+        <v>1000</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1052</v>
+        <v>1001</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>6</v>
@@ -8721,25 +10846,25 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1053</v>
+        <v>1002</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1054</v>
+        <v>1003</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1055</v>
+        <v>1004</v>
       </c>
       <c r="F30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1056</v>
+        <v>1005</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1057</v>
+        <v>1006</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1058</v>
+        <v>1007</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>6</v>
@@ -8747,13 +10872,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1059</v>
+        <v>1008</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1060</v>
+        <v>1009</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1061</v>
+        <v>1010</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>6</v>
@@ -8761,25 +10886,25 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1062</v>
+        <v>1011</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1063</v>
+        <v>1012</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1064</v>
+        <v>1013</v>
       </c>
       <c r="F33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1065</v>
+        <v>1014</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1066</v>
+        <v>1015</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1067</v>
+        <v>1016</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>6</v>
@@ -8787,25 +10912,25 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>1068</v>
+        <v>1017</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1069</v>
+        <v>1018</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1070</v>
+        <v>1019</v>
       </c>
       <c r="F35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>1071</v>
+        <v>1020</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1072</v>
+        <v>1021</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1073</v>
+        <v>1022</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -8813,25 +10938,25 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>1074</v>
+        <v>1023</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1075</v>
+        <v>1024</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1076</v>
+        <v>1025</v>
       </c>
       <c r="F37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>1077</v>
+        <v>1026</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1078</v>
+        <v>1027</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1079</v>
+        <v>1028</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -8839,25 +10964,25 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>1080</v>
+        <v>1029</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1081</v>
+        <v>1030</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1082</v>
+        <v>1031</v>
       </c>
       <c r="F39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>1083</v>
+        <v>1032</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1084</v>
+        <v>1033</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1085</v>
+        <v>1034</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -8865,25 +10990,25 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>1086</v>
+        <v>1035</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1087</v>
+        <v>1036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1088</v>
+        <v>1037</v>
       </c>
       <c r="F41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>1089</v>
+        <v>1038</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1090</v>
+        <v>1039</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1091</v>
+        <v>1040</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -8891,25 +11016,25 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>1092</v>
+        <v>1041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1093</v>
+        <v>1042</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1094</v>
+        <v>1043</v>
       </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>1095</v>
+        <v>1044</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1096</v>
+        <v>1045</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1097</v>
+        <v>1046</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -8917,25 +11042,25 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>1098</v>
+        <v>1047</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1099</v>
+        <v>1048</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1100</v>
+        <v>1049</v>
       </c>
       <c r="F45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>1101</v>
+        <v>1050</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1102</v>
+        <v>1051</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1103</v>
+        <v>1052</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -8943,13 +11068,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>1104</v>
+        <v>1053</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1105</v>
+        <v>1054</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1106</v>
+        <v>1055</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -8957,13 +11082,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>1107</v>
+        <v>1056</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1108</v>
+        <v>1057</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1109</v>
+        <v>1058</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -8971,13 +11096,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>1110</v>
+        <v>1059</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1111</v>
+        <v>1060</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1112</v>
+        <v>1061</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -8985,13 +11110,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>1113</v>
+        <v>1062</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1114</v>
+        <v>1063</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1115</v>
+        <v>1064</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -8999,13 +11124,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>1116</v>
+        <v>1065</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1117</v>
+        <v>1066</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1118</v>
+        <v>1067</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -9013,13 +11138,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>1119</v>
+        <v>1068</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1120</v>
+        <v>1069</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1121</v>
+        <v>1070</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -9027,13 +11152,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>1122</v>
+        <v>1071</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1123</v>
+        <v>1072</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1124</v>
+        <v>1073</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -9041,13 +11166,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>1125</v>
+        <v>1074</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1126</v>
+        <v>1075</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1127</v>
+        <v>1076</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -9055,13 +11180,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>1128</v>
+        <v>1077</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1129</v>
+        <v>1078</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1130</v>
+        <v>1079</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -9069,13 +11194,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>1131</v>
+        <v>1080</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1132</v>
+        <v>1081</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1133</v>
+        <v>1082</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -9083,13 +11208,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>1134</v>
+        <v>1083</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1135</v>
+        <v>1084</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1136</v>
+        <v>1085</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -9097,15 +11222,3918 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F162"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="49.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="49.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>1137</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B17" s="0" t="s">
         <v>1138</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D17" s="0" t="s">
         <v>1139</v>
       </c>
+      <c r="F17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>1237</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>1260</v>
+      </c>
       <c r="F58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>1333</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F97" s="1"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>1392</v>
+      </c>
+      <c r="F103" s="1"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D104" s="0" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D105" s="0" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="0" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F115" s="1"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D116" s="0" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D117" s="0" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D118" s="0" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D119" s="0" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D120" s="0" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D121" s="0" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F121" s="1"/>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D122" s="0" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D123" s="0" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D125" s="0" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D126" s="0" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D127" s="0" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F127" s="1"/>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B128" s="0" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D128" s="0" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B129" s="0" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D129" s="0" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D130" s="0" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D131" s="0" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="0" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D132" s="0" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="0" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B133" s="0" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D133" s="0" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F133" s="1"/>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="0" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D134" s="0" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B135" s="0" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D135" s="0" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="0" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B136" s="0" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D136" s="0" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="0" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B137" s="0" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D137" s="0" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="0" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B138" s="0" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D138" s="0" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="0" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B139" s="0" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F139" s="1"/>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="0" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B140" s="0" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D140" s="0" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="0" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B141" s="0" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D141" s="0" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="0" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B142" s="0" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D142" s="0" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="0" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B143" s="0" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D143" s="0" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="0" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D145" s="0" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F145" s="1"/>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B146" s="0" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D146" s="0" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D149" s="0" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D150" s="0" t="s">
+        <v>1531</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D151" s="0" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F151" s="1"/>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D152" s="0" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D153" s="0" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B154" s="0" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D154" s="0" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="0" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B155" s="0" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D155" s="0" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="0" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B156" s="0" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D156" s="0" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="0" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B157" s="0" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D157" s="0" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F157" s="1"/>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B158" s="0" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D158" s="0" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B159" s="0" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D159" s="0" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="0" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B160" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D160" s="0" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="0" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B161" s="0" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D161" s="0" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="0" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B162" s="0" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D162" s="0" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F120"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="65.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="93.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="64.74"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>1664</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>1691</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>1694</v>
+      </c>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>1712</v>
+      </c>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>1715</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>1721</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>1730</v>
+      </c>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>1733</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>1736</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>1739</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>1742</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>1745</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>1751</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>1754</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>1760</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>1763</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>1772</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>1775</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>1778</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>1790</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>1799</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>1805</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>1808</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>1814</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>1817</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>1823</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>1838</v>
+      </c>
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>1850</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F97" s="1"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>1862</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F103" s="1"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D104" s="0" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D105" s="0" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="0" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>1895</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>1907</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F115" s="1"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D116" s="0" t="s">
+        <v>1913</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D117" s="0" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D118" s="0" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D119" s="0" t="s">
+        <v>1922</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D120" s="0" t="s">
+        <v>1925</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>6</v>
       </c>
     </row>
